--- a/artfynd/A 11348-2022 artfynd.xlsx
+++ b/artfynd/A 11348-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129879028</v>
       </c>
       <c r="B2" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11348-2022 artfynd.xlsx
+++ b/artfynd/A 11348-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129879028</v>
       </c>
       <c r="B2" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130101260</v>
       </c>
       <c r="B3" t="n">
-        <v>58461</v>
+        <v>58546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11348-2022 artfynd.xlsx
+++ b/artfynd/A 11348-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129879028</v>
       </c>
       <c r="B2" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
